--- a/Assets/GameResource/Excel/法术表.xlsx
+++ b/Assets/GameResource/Excel/法术表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5342A490-5618-4942-8372-7F7F16A25B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE9C0B1-3D1E-47EB-B693-26C5CC88CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12750" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpellInfo" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,6 +72,18 @@
   </si>
   <si>
     <t>三段使用次数，基础伤害6，击杀敌人解锁后续段数，伤害倍率x1,x1.5,x2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法术闪电箭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标寻址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -397,14 +409,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="67.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="67.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,10 +428,13 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -431,8 +447,11 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -443,10 +462,13 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -457,6 +479,9 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
     </row>
